--- a/excel/ALCOHOL.xlsx
+++ b/excel/ALCOHOL.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
   <si>
     <t>Match</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>League Name "Alcohol League Cup 4"</t>
+  </si>
+  <si>
+    <t>https://urlshort.asia/zRKDy</t>
   </si>
 </sst>
 </file>
@@ -654,15 +657,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="32"/>
+      <c r="E2" s="32" t="s">
+        <v>35</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
@@ -675,12 +680,14 @@
         <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="32"/>
+      <c r="E3" s="32" t="s">
+        <v>35</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
@@ -690,15 +697,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="32" t="s">
+        <v>35</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
@@ -708,15 +717,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="32"/>
+      <c r="E5" s="32" t="s">
+        <v>35</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
@@ -726,15 +737,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="32"/>
+      <c r="E6" s="32" t="s">
+        <v>35</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="F51" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="150" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <pageSetup paperSize="150" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/excel/ALCOHOL.xlsx
+++ b/excel/ALCOHOL.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>Match</t>
   </si>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t>League Name "Alcohol League Cup 4"</t>
-  </si>
-  <si>
-    <t>https://urlshort.asia/zRKDy</t>
   </si>
 </sst>
 </file>
@@ -657,17 +654,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="32" t="s">
-        <v>35</v>
-      </c>
+      <c r="E2" s="32"/>
       <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
@@ -680,14 +675,12 @@
         <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="32" t="s">
-        <v>35</v>
-      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
@@ -697,17 +690,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="32" t="s">
-        <v>35</v>
-      </c>
+      <c r="E4" s="32"/>
       <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
@@ -717,17 +708,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="32" t="s">
-        <v>35</v>
-      </c>
+      <c r="E5" s="32"/>
       <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
@@ -737,17 +726,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="32" t="s">
-        <v>35</v>
-      </c>
+      <c r="E6" s="32"/>
       <c r="F6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1203,11 +1190,8 @@
       <c r="F51" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="150" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId2"/>
+  <pageSetup paperSize="150" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
